--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486478_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486478_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6551</v>
+        <v>6.1486</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6944</v>
+        <v>4.4962</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9607</v>
+        <v>1.6525</v>
       </c>
       <c r="G2" t="n">
         <v>4.7146</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>1.853</v>
+        <v>1.3465</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9421</v>
+        <v>0.7439</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9109</v>
+        <v>0.6026</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7915</v>
+        <v>4.5095</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3623</v>
+        <v>2.6796</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4292</v>
+        <v>1.8299</v>
       </c>
       <c r="G3" t="n">
         <v>2.9918</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2003</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2139</v>
+        <v>0.1034</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0136</v>
+        <v>0.4143</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7043</v>
+        <v>4.0125</v>
       </c>
       <c r="E4" t="n">
         <v>1.8235</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8807</v>
+        <v>2.189</v>
       </c>
       <c r="G4" t="n">
         <v>4.3688</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2295</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>0.2656</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4951</v>
+        <v>-0.1869</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3402</v>
+        <v>1.4598</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7472</v>
+        <v>-2.5042</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0874</v>
+        <v>3.9641</v>
       </c>
       <c r="G5" t="n">
         <v>-2.323</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3789</v>
+        <v>1.4985</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3447</v>
+        <v>0.5876</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0342</v>
+        <v>0.9109</v>
       </c>
       <c r="V5" t="n">
         <v>0.5443</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.995</v>
+        <v>1.067</v>
       </c>
       <c r="E6" t="n">
-        <v>0.336</v>
+        <v>-1.2843</v>
       </c>
       <c r="F6" t="n">
-        <v>0.659</v>
+        <v>2.3513</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.447</v>
+        <v>4.0246</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6264</v>
+        <v>3.4429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0734</v>
+        <v>0.5817</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1492</v>
+        <v>4.3363</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1642</v>
+        <v>3.0143</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0151</v>
+        <v>1.322</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5962</v>
+        <v>-0.3117</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4621</v>
+        <v>0.4286</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0583</v>
+        <v>-0.7403</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7401</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-5.6552</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>2.6101</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1029</v>
+        <v>0.4572</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2091</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0945</v>
+        <v>0.2481</v>
       </c>
       <c r="V6" t="n">
+        <v>-0.3698</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1745</v>
+      </c>
+      <c r="X6" t="n">
         <v>-0.1952</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.1952</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.3904</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6661</v>
+        <v>0.7668</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7575</v>
+        <v>0.2927</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4236</v>
+        <v>0.474</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7955</v>
+        <v>-0.447</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3115</v>
+        <v>0.6264</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.107</v>
+        <v>-1.0734</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8679</v>
+        <v>0.1492</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8828</v>
+        <v>0.1642</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.7507</v>
+        <v>-0.0151</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9277</v>
+        <v>-0.5962</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4286</v>
+        <v>0.4621</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3563</v>
+        <v>-1.0583</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5676</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8564</v>
+        <v>-0.3311</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4627</v>
+        <v>-0.0517</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3937</v>
+        <v>-0.2794</v>
       </c>
       <c r="V7" t="n">
-        <v>3.2154</v>
+        <v>-0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2154</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2175</v>
+        <v>-0.1418</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3838</v>
+        <v>-1.8873</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1664</v>
+        <v>1.7455</v>
       </c>
       <c r="G8" t="n">
-        <v>4.0246</v>
+        <v>-1.7955</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4429</v>
+        <v>2.3115</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5817</v>
+        <v>-4.107</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3363</v>
+        <v>-0.8679</v>
       </c>
       <c r="K8" t="n">
-        <v>3.0143</v>
+        <v>1.8828</v>
       </c>
       <c r="L8" t="n">
-        <v>1.322</v>
+        <v>-2.7507</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3117</v>
+        <v>-0.9277</v>
       </c>
       <c r="N8" t="n">
         <v>0.4286</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7403</v>
+        <v>-1.3563</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.0451</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.6552</v>
+        <v>-4.5676</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6101</v>
+        <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8272</v>
+        <v>1.0485</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8904</v>
+        <v>0.3329</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.7156</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3698</v>
+        <v>3.2154</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1745</v>
+        <v>3.2154</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>J. LOPEZ SANTANA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6313</v>
+        <v>-0.1783</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3948</v>
+        <v>-0.8525</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2365</v>
+        <v>0.6742</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6701</v>
+        <v>-0.8753</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2773</v>
+        <v>2.348</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3928</v>
+        <v>-3.2233</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0455</v>
+        <v>-0.5461</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9307</v>
+        <v>1.5544</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1147</v>
+        <v>-2.1005</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6247</v>
+        <v>-0.3292</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3466</v>
+        <v>0.7936</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2781</v>
+        <v>-1.1228</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.305</v>
+        <v>1.305</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0616</v>
+        <v>-0.6081</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5396</v>
+        <v>-0.3064</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6012</v>
+        <v>-0.3016</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANTANA</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8172</v>
+        <v>-0.5273</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3681</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5508999999999999</v>
+        <v>-0.0207</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8753</v>
+        <v>1.6701</v>
       </c>
       <c r="H10" t="n">
-        <v>2.348</v>
+        <v>1.2773</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2233</v>
+        <v>0.3928</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5461</v>
+        <v>1.0455</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5544</v>
+        <v>0.9307</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1005</v>
+        <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3292</v>
+        <v>0.6247</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7936</v>
+        <v>0.3466</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1228</v>
+        <v>0.2781</v>
       </c>
       <c r="P10" t="n">
-        <v>1.305</v>
+        <v>-1.305</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2469</v>
+        <v>0.0424</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.822</v>
+        <v>0.4278</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4249</v>
+        <v>-0.3854</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7413</v>
+        <v>-1.3444</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1594</v>
+        <v>1.4946</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9007</v>
+        <v>-2.839</v>
       </c>
       <c r="G11" t="n">
         <v>1.1661</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0825</v>
+        <v>-0.6856</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.466</v>
+        <v>-0.4044</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2599</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.7449</v>
+        <v>15.7724</v>
       </c>
       <c r="E12" t="n">
-        <v>2.724199999999999</v>
+        <v>3.7517</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0207</v>
+        <v>12.0208</v>
       </c>
       <c r="G12" t="n">
         <v>13.4952</v>
@@ -1360,7 +1360,7 @@
         <v>17.3203</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.825000000000001</v>
+        <v>-3.825</v>
       </c>
       <c r="J12" t="n">
         <v>14.3648</v>
@@ -1369,10 +1369,10 @@
         <v>11.9539</v>
       </c>
       <c r="L12" t="n">
-        <v>2.410700000000001</v>
+        <v>2.4107</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8696999999999997</v>
+        <v>-0.8696999999999996</v>
       </c>
       <c r="N12" t="n">
         <v>5.366000000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-6.2357</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.087500000000001</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.4005</v>
@@ -1390,22 +1390,22 @@
         <v>16.3132</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3374</v>
+        <v>3.364599999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0035</v>
+        <v>2.031</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3339</v>
+        <v>1.3338</v>
       </c>
       <c r="V12" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="W12" t="n">
         <v>4.7565</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.7564</v>
+        <v>-4.756399999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1377</v>
+        <v>2.6156</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4881</v>
+        <v>0.9351</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6497</v>
+        <v>1.6805</v>
       </c>
       <c r="G13" t="n">
         <v>2.8502</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7125</v>
+        <v>-0.2346</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.548</v>
+        <v>-0.1009</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1645</v>
+        <v>-0.1337</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CAICEDO SANCHEZ</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9132</v>
+        <v>0.0559</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1118</v>
+        <v>0.4775</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8014</v>
+        <v>-0.4217</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.0376</v>
+        <v>-0.5565</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.8344</v>
+        <v>-0.1277</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2032</v>
+        <v>-0.4287</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.7465</v>
+        <v>0.093</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.5385</v>
+        <v>0.0547</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2079</v>
+        <v>0.0382</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2911</v>
+        <v>-0.6495</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2959</v>
+        <v>-0.1825</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0047</v>
+        <v>-0.467</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8409</v>
+        <v>0.3725</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7282</v>
+        <v>0.3845</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1127</v>
+        <v>-0.012</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9347</v>
+        <v>-0.1952</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.1952</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>M. CAICEDO SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0444</v>
+        <v>-0.239</v>
       </c>
       <c r="E15" t="n">
-        <v>0.254</v>
+        <v>-0.6706</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2984</v>
+        <v>0.4316</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5565</v>
+        <v>-3.0376</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1277</v>
+        <v>-2.8344</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4287</v>
+        <v>-0.2032</v>
       </c>
       <c r="J15" t="n">
-        <v>0.093</v>
+        <v>-1.7465</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0547</v>
+        <v>-1.5385</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0382</v>
+        <v>-0.2079</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6495</v>
+        <v>-1.2911</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1825</v>
+        <v>-1.2959</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.467</v>
+        <v>0.0047</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2723</v>
+        <v>-0.3112</v>
       </c>
       <c r="T15" t="n">
-        <v>0.161</v>
+        <v>-0.0541</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1113</v>
+        <v>-0.2572</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1952</v>
+        <v>0.9347</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1952</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2164</v>
+        <v>-0.8621</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3847</v>
+        <v>-0.2905</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1683</v>
+        <v>-0.5716</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8471</v>
+        <v>-0.3983</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2645</v>
+        <v>-1.8095</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1116</v>
+        <v>1.4112</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1433</v>
+        <v>1.4729</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4599</v>
+        <v>-0.6141</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.6032</v>
+        <v>2.087</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7038</v>
+        <v>-1.8712</v>
       </c>
       <c r="N16" t="n">
         <v>-1.1954</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4916</v>
+        <v>-0.6758</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3702</v>
+        <v>-1.3534</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5432</v>
+        <v>-0.7607</v>
       </c>
       <c r="U16" t="n">
-        <v>0.827</v>
+        <v>-0.5927</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7395</v>
+        <v>2.6297</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3904</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4173</v>
+        <v>-0.9079</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0934</v>
+        <v>-0.6499</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3239</v>
+        <v>-0.2581</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6708</v>
+        <v>-0.8925</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6782</v>
+        <v>-2.8496</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3491</v>
+        <v>1.9571</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4305</v>
+        <v>0.0423</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4417</v>
+        <v>-1.8702</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0112</v>
+        <v>1.9125</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1013</v>
+        <v>-0.9348</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7635</v>
+        <v>-0.9794</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3379</v>
+        <v>0.0446</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4487</v>
+        <v>0.4621</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5636</v>
+        <v>0.3954</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1149</v>
+        <v>0.0667</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4747</v>
+        <v>-0.91</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6257</v>
+        <v>-1.8318</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.849</v>
+        <v>0.9217</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3983</v>
+        <v>-0.8471</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8095</v>
+        <v>0.2645</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4112</v>
+        <v>-1.1116</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4729</v>
+        <v>-0.1433</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6141</v>
+        <v>1.4599</v>
       </c>
       <c r="L18" t="n">
-        <v>2.087</v>
+        <v>-1.6032</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8712</v>
+        <v>-0.7038</v>
       </c>
       <c r="N18" t="n">
         <v>-1.1954</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6758</v>
+        <v>0.4916</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7401</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9661</v>
+        <v>0.6766</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0959</v>
+        <v>0.0961</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8702</v>
+        <v>0.5804</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6297</v>
+        <v>-0.7395</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2599</v>
+        <v>0.3904</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7519</v>
+        <v>-0.9376</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4322</v>
+        <v>-0.4287</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3197</v>
+        <v>-0.5089</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8925</v>
+        <v>-0.6708</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8496</v>
+        <v>0.6782</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9571</v>
+        <v>-1.3491</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0423</v>
+        <v>0.4305</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8702</v>
+        <v>1.4417</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9125</v>
+        <v>-1.0112</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9348</v>
+        <v>-1.1013</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9794</v>
+        <v>-0.7635</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0446</v>
+        <v>-0.3379</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3819</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3869</v>
+        <v>0.2283</v>
       </c>
       <c r="U19" t="n">
-        <v>0.005</v>
+        <v>-0.2998</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BERGSTEDT</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8216</v>
+        <v>-2.5172</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0998</v>
+        <v>-0.8189</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9214</v>
+        <v>-1.6983</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5277</v>
+        <v>-3.3297</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.475</v>
+        <v>-2.3113</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0527</v>
+        <v>-1.0184</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6303</v>
+        <v>-0.8314</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7451</v>
+        <v>-0.8514</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1147</v>
+        <v>0.0199</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8974</v>
+        <v>-2.4983</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.73</v>
+        <v>-1.4599</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1674</v>
+        <v>-1.0383</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0329</v>
+        <v>0.0502</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0791</v>
+        <v>-0.1826</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0463</v>
+        <v>0.2328</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5443</v>
+        <v>-0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3491</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4594</v>
+        <v>-2.5362</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4836</v>
+        <v>-3.4465</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9758</v>
+        <v>0.9104</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.3297</v>
+        <v>-0.9498</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3113</v>
+        <v>-1.2957</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0184</v>
+        <v>0.3459</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8314</v>
+        <v>-0.7776</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8514</v>
+        <v>-0.3983</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0199</v>
+        <v>-0.3793</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4983</v>
+        <v>-0.1723</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4599</v>
+        <v>-0.8974</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0383</v>
+        <v>0.7251</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5225</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>0.108</v>
+        <v>-0.4563</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1526</v>
+        <v>-0.4939</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0446</v>
+        <v>0.0375</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9554</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>J. BERGSTEDT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1489</v>
+        <v>-2.5616</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6796</v>
+        <v>-0.7943</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4693</v>
+        <v>-1.7673</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6602</v>
+        <v>-2.5277</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.1782</v>
+        <v>-1.475</v>
       </c>
       <c r="I22" t="n">
-        <v>1.518</v>
+        <v>-1.0527</v>
       </c>
       <c r="J22" t="n">
-        <v>0.823</v>
+        <v>-0.6303</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4354</v>
+        <v>-0.7451</v>
       </c>
       <c r="L22" t="n">
-        <v>2.2583</v>
+        <v>0.1147</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4832</v>
+        <v>-1.8974</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7429</v>
+        <v>-0.73</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7403</v>
+        <v>-1.1674</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3136</v>
+        <v>0.2929</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3699</v>
+        <v>0.1851</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0564</v>
+        <v>0.1078</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>-0.5443</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>-0.3491</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1622</v>
+        <v>-2.7327</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1581</v>
+        <v>-2.2326</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0042</v>
+        <v>-0.5001</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4753</v>
+        <v>-1.6602</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0833</v>
+        <v>-3.1782</v>
       </c>
       <c r="I23" t="n">
-        <v>0.608</v>
+        <v>1.518</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0134</v>
+        <v>0.823</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8879</v>
+        <v>-1.4354</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9013</v>
+        <v>2.2583</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4887</v>
+        <v>-2.4832</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1954</v>
+        <v>-1.7429</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2933</v>
+        <v>-0.7403</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R23" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8169</v>
+        <v>-0.8974</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0036</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8205</v>
+        <v>0.0255</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2992</v>
+        <v>-3.2123</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1171</v>
+        <v>-2.2698</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8179</v>
+        <v>-0.9425</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9498</v>
+        <v>-1.4753</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2957</v>
+        <v>-2.0833</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3459</v>
+        <v>0.608</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7776</v>
+        <v>0.0134</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3983</v>
+        <v>-0.8879</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3793</v>
+        <v>0.9013</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1723</v>
+        <v>-1.4887</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8974</v>
+        <v>-1.1954</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7251</v>
+        <v>-0.2933</v>
       </c>
       <c r="P24" t="n">
-        <v>-0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2194</v>
+        <v>-0.867</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1644</v>
+        <v>-0.1081</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0549</v>
+        <v>-0.7589</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2362,10 +2362,10 @@
         <v>-14.7451</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.0207</v>
+        <v>-12.021</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7244</v>
+        <v>-2.7243</v>
       </c>
       <c r="G25" t="n">
         <v>-13.4953</v>
@@ -2377,10 +2377,10 @@
         <v>3.8249</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8696</v>
+        <v>0.8696000000000003</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.3664</v>
+        <v>-5.366400000000001</v>
       </c>
       <c r="L25" t="n">
         <v>6.235600000000001</v>
@@ -2404,16 +2404,16 @@
         <v>17.4005</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.3374</v>
+        <v>-2.3371</v>
       </c>
       <c r="T25" t="n">
         <v>-1.3338</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0035</v>
+        <v>-1.0036</v>
       </c>
       <c r="V25" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="W25" t="n">
         <v>4.756399999999999</v>
